--- a/CEP_TestCases/Players_Module_Test_Cases_Final.xlsx
+++ b/CEP_TestCases/Players_Module_Test_Cases_Final.xlsx
@@ -5331,7 +5331,7 @@
     </row>
     <row r="152" xml:space="preserve">
       <c r="A152" t="str">
-        <v>PLR-EXP-01</v>
+        <v>PLR-EXP-26</v>
       </c>
       <c r="B152" t="str">
         <v>Quiz Player</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="153" xml:space="preserve">
       <c r="A153" t="str">
-        <v>PLR-EXP-02</v>
+        <v>PLR-EXP-27</v>
       </c>
       <c r="B153" t="str">
         <v>Quiz Player</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="154" xml:space="preserve">
       <c r="A154" t="str">
-        <v>PLR-EXP-03</v>
+        <v>PLR-EXP-28</v>
       </c>
       <c r="B154" t="str">
         <v>Video Player</v>
@@ -5431,7 +5431,7 @@
     </row>
     <row r="155" xml:space="preserve">
       <c r="A155" t="str">
-        <v>PLR-EXP-04</v>
+        <v>PLR-EXP-29</v>
       </c>
       <c r="B155" t="str">
         <v>Worksheet Player</v>
